--- a/clino_hk0_plane_hkl_accessible.xlsx
+++ b/clino_hk0_plane_hkl_accessible.xlsx
@@ -503,7 +503,7 @@
       <c r="I2" t="n">
         <v>13</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -535,7 +535,7 @@
       <c r="I3" t="n">
         <v>13</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -567,7 +567,7 @@
       <c r="I4" t="n">
         <v>13</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -599,7 +599,7 @@
       <c r="I5" t="n">
         <v>13</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" t="b">
         <v>1</v>
       </c>
     </row>
@@ -631,7 +631,7 @@
       <c r="I6" t="n">
         <v>13</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -663,7 +663,7 @@
       <c r="I7" t="n">
         <v>13</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -695,7 +695,7 @@
       <c r="I8" t="n">
         <v>13</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -727,7 +727,7 @@
       <c r="I9" t="n">
         <v>13</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" t="b">
         <v>1</v>
       </c>
     </row>
